--- a/partner_results/unknown_digitrubber/ClassMissingCurationStatus_unknown_digitrubber.xlsx
+++ b/partner_results/unknown_digitrubber/ClassMissingCurationStatus_unknown_digitrubber.xlsx
@@ -478,7 +478,11 @@
           <t>Lars M Vogt</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Definition not available</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
   </sheetData>
